--- a/artfynd/A 32100-2025 artfynd.xlsx
+++ b/artfynd/A 32100-2025 artfynd.xlsx
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743055</v>
+        <v>122743056</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- V, Jmt</t>
+          <t>Bastuliden NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490639</v>
+        <v>490642</v>
       </c>
       <c r="R2" t="n">
         <v>7135486</v>
@@ -776,42 +776,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743056</v>
+        <v>122743055</v>
       </c>
       <c r="B3" t="n">
-        <v>80438</v>
+        <v>80493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastuliden NÖ, Jmt</t>
+          <t>Renskinns- V, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490642</v>
+        <v>490639</v>
       </c>
       <c r="R3" t="n">
         <v>7135486</v>

--- a/artfynd/A 32100-2025 artfynd.xlsx
+++ b/artfynd/A 32100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743056</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>